--- a/new_bates_manifest.xlsx
+++ b/new_bates_manifest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,7 +587,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D:/Download\Aetna card (1).pdf</t>
+          <t>D:/Download\AFER RACHAT LIAM.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D:/Download\Aetna card (2).pdf</t>
+          <t>D:/Download\airport to inn 18may.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D:/Download\Aetna card (3).pdf</t>
+          <t>D:/Download\airport to la quinta hotel 24may.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D:/Download\Aetna card.pdf</t>
+          <t>D:/Download\airway inn 17may.pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D:/Download\AFER RACHAT LIAM.pdf</t>
+          <t>D:/Download\alliant apr.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D:/Download\airport to inn 18may.pdf</t>
+          <t>D:/Download\alliant june.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D:/Download\airport to la quinta hotel 24may.pdf</t>
+          <t>D:/Download\alliant may.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D:/Download\airway inn 17may.pdf</t>
+          <t>D:/Download\asos.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D:/Download\alliant apr.pdf</t>
+          <t>D:/Download\Attestation Prise en charge ludmila Liban.pdf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D:/Download\alliant june.pdf</t>
+          <t>D:/Download\b5aed10a5096f680ff8515cdf7b561a36764dc8a.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D:/Download\alliant may.pdf</t>
+          <t>D:/Download\Booking-Conditions.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D:/Download\asos.pdf</t>
+          <t>D:/Download\bromont tickets.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D:/Download\Attestation Prise en charge ludmila Liban.pdf</t>
+          <t>D:/Download\car1.pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D:/Download\b5aed10a5096f680ff8515cdf7b561a36764dc8a.pdf</t>
+          <t>D:/Download\car2.pdf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D:/Download\Booking-Conditions.pdf</t>
+          <t>D:/Download\car3.pdf</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>D:/Download\bromont tickets.pdf</t>
+          <t>D:/Download\car4.pdf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D:/Download\car1.pdf</t>
+          <t>D:/Download\car5.pdf</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>D:/Download\car2.pdf</t>
+          <t>D:/Download\car6.pdf</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>D:/Download\car3.pdf</t>
+          <t>D:/Download\ClaimStatement.pdf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>D:/Download\car4.pdf</t>
+          <t>D:/Download\Complete_with_Docusign_32-80_30th_Street_Apt.pdf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>D:/Download\car5.pdf</t>
+          <t>D:/Download\Complete_with_Docusign_Complete_with_Docusig.pdf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>D:/Download\car6.pdf</t>
+          <t>D:/Download\coned.pdf</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D:/Download\ClaimStatement.pdf</t>
+          <t>D:/Download\ConfirmationForm.pdf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>D:/Download\Complete_with_Docusign_32-80_30th_Street_Apt.pdf</t>
+          <t>D:/Download\Consonants Pretest Handout.pdf</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>D:/Download\Complete_with_Docusign_Complete_with_Docusig.pdf</t>
+          <t>D:/Download\Country-Specific-Conditions.pdf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D:/Download\coned.pdf</t>
+          <t>D:/Download\Credit Card Payment Form-Filled.pdf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D:/Download\ConfirmationForm.pdf</t>
+          <t>D:/Download\cv_nico_2014.pdf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>D:/Download\Consonants Pretest Handout.pdf</t>
+          <t>D:/Download\cv_nico_last_year.pdf</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>D:/Download\Country-Specific-Conditions.pdf</t>
+          <t>D:/Download\DecViaRegion_250007DVIE042858Z_17052025_143930.pdf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D:/Download\Credit Card Payment Form-Filled.pdf</t>
+          <t>D:/Download\delta cancelled flight.pdf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D:/Download\cv_nico_2014.pdf</t>
+          <t>D:/Download\delta flight cancellation email.pdf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>D:/Download\cv_nico_last_year.pdf</t>
+          <t>D:/Download\demande-rachat-total.pdf</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D:/Download\DecViaRegion_250007DVIE042858Z_17052025_143930.pdf</t>
+          <t>D:/Download\document.pdf</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D:/Download\delta cancelled flight.pdf</t>
+          <t>D:/Download\Earnings - Dayforce6.pdf</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D:/Download\delta flight cancellation email.pdf</t>
+          <t>D:/Download\escape.pdf</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D:/Download\demande-rachat-total.pdf</t>
+          <t>D:/Download\facture.pdf</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D:/Download\document.pdf</t>
+          <t>D:/Download\fidelity signature only.pdf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D:/Download\Earnings - Dayforce6.pdf</t>
+          <t>D:/Download\form1583_3483561_2525_1755131548.pdf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>D:/Download\escape.pdf</t>
+          <t>D:/Download\frontier.pdf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D:/Download\facture.pdf</t>
+          <t>D:/Download\fundrise_tax_package_2024.pdf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D:/Download\fidelity signature only.pdf</t>
+          <t>D:/Download\Future_Shock_Retrofit_Compatibility_Tech_Bulletin.pdf</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D:/Download\form1583_3483561_2525_1755131548.pdf</t>
+          <t>D:/Download\inn to airport 18May.pdf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D:/Download\frontier.pdf</t>
+          <t>D:/Download\intraoral-therapy.pdf</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D:/Download\fundrise_tax_package_2024.pdf</t>
+          <t>D:/Download\josh boarding AC874.pdf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D:/Download\Future_Shock_Retrofit_Compatibility_Tech_Bulletin.pdf</t>
+          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a (1).pdf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D:/Download\inn to airport 18May.pdf</t>
+          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a (2).pdf</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>D:/Download\intraoral-therapy.pdf</t>
+          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a (3).pdf</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>D:/Download\josh boarding AC874.pdf</t>
+          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a.pdf</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a (1).pdf</t>
+          <t>D:/Download\la quinta 24May2025.pdf</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a (2).pdf</t>
+          <t>D:/Download\las rocas 17may.pdf</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a (3).pdf</t>
+          <t>D:/Download\mv82 (1).pdf</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>D:/Download\KM8K1CAAXJU135958-26bab9e63bddc0a.pdf</t>
+          <t>D:/Download\mv82.pdf</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>D:/Download\la quinta 24May2025.pdf</t>
+          <t>D:/Download\Nicolas Leveque CustomerVF.pdf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>D:/Download\las rocas 17may.pdf</t>
+          <t>D:/Download\Nicolas Leveque Resume.pdf</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>D:/Download\mv82 (1).pdf</t>
+          <t>D:/Download\Nicolas Leveque's 2024 Tax Return.pdf</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>D:/Download\mv82.pdf</t>
+          <t>D:/Download\NicolasLeveque-2024-SSB-Booking (1).pdf</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>D:/Download\Nicolas Leveque CustomerVF.pdf</t>
+          <t>D:/Download\NicolasLeveque-2024-SSB-Booking.pdf</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>D:/Download\Nicolas Leveque Resume.pdf</t>
+          <t>D:/Download\office rental form  Angela Kontis.pdf</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>D:/Download\Nicolas Leveque's 2024 Tax Return.pdf</t>
+          <t>D:/Download\Office Rental Form 2022 (2) (2) (1).pdf</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D:/Download\NicolasLeveque-2024-SSB-Booking (1).pdf</t>
+          <t>D:/Download\parking-voucher.pdf</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D:/Download\NicolasLeveque-2024-SSB-Booking.pdf</t>
+          <t>D:/Download\Pharmacy Patient Authorization Form v2_encrypted_.pdf</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D:/Download\office rental form  Angela Kontis.pdf</t>
+          <t>D:/Download\rdv-consulat.pdf</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D:/Download\Office Rental Form 2022 (2) (2) (1).pdf</t>
+          <t>D:/Download\regal.pdf</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>D:/Download\parking-voucher.pdf</t>
+          <t>D:/Download\TaxForm.pdf</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>D:/Download\Pharmacy Patient Authorization Form v2_encrypted_.pdf</t>
+          <t>D:/Download\TaxStatement_2025_1099B_DIV_268011248594651.pdf</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>D:/Download\rdv-consulat.pdf</t>
+          <t>D:/Download\Temporary_Photo_Document.pdf</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>D:/Download\regal.pdf</t>
+          <t>D:/Download\Ticket-New-York-Ny-Binghamton-Ny-3217585813.pdf</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>D:/Download\TaxForm.pdf</t>
+          <t>D:/Download\Title or Lien Status (MV-913).pdf</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>D:/Download\TaxStatement_2025_1099B_DIV_268011248594651.pdf</t>
+          <t>D:/Download\tucson-2017.pdf</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>D:/Download\Temporary_Photo_Document.pdf</t>
+          <t>D:/Download\tucson2018.pdf</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>D:/Download\Ticket-New-York-Ny-Binghamton-Ny-3217585813.pdf</t>
+          <t>D:/Download\united replacement flight.pdf</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>D:/Download\Title or Lien Status (MV-913).pdf</t>
+          <t>D:/Download\us passport.pdf</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>D:/Download\tucson-2017.pdf</t>
+          <t>D:/Download\virtual data card dupixent.pdf</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>D:/Download\tucson2018.pdf</t>
+          <t>D:/Download\Voiced &amp; voiceless sounds handout.pdf</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>D:/Download\united replacement flight.pdf</t>
+          <t>D:/Download\w2 nicolas 2023.pdf</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>D:/Download\us passport.pdf</t>
+          <t>D:/Download\w2 nicolas 2024.pdf</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>D:/Download\virtual data card dupixent.pdf</t>
+          <t>D:/Download\W2 Nicolas.pdf</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>D:/Download\Voiced &amp; voiceless sounds handout.pdf</t>
+          <t>D:/Download\waiver of rigth.pdf</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>D:/Download\w2 nicolas 2023.pdf</t>
+          <t>D:/Download\wellsfargo_jobspec.pdf</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>D:/Download\w2 nicolas 2024.pdf</t>
+          <t>D:/Download\fidelity\sl-active-money-sample.pdf</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -1547,58 +1547,10 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>D:/Download\W2 Nicolas.pdf</t>
+          <t>D:/Download\fidelity\switch-form-for-fidelity-personal-pension-provided-by-standard-life.pdf</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>D:/Download\waiver of rigth.pdf</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>D:/Download\wellsfargo_jobspec.pdf</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>D:/Download\fidelity\sl-active-money-sample.pdf</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>D:/Download\fidelity\switch-form-for-fidelity-personal-pension-provided-by-standard-life.pdf</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
         <is>
           <t>DOC</t>
         </is>
